--- a/public/products.xlsx
+++ b/public/products.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GAYATRI\OneDrive\Desktop\ecommerce-tyre\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFAFF43-FB45-4EF7-942F-DC898E262D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D9F493-C0C1-463E-AB38-5DDCC230AA68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="10080" activeTab="1" xr2:uid="{753CF4C0-B9A8-4CBB-A6D1-A0D84C211A7C}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="10080" activeTab="4" xr2:uid="{753CF4C0-B9A8-4CBB-A6D1-A0D84C211A7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Accessories" sheetId="1" r:id="rId1"/>
     <sheet name="Tyres" sheetId="2" r:id="rId2"/>
     <sheet name="Batteries" sheetId="3" r:id="rId3"/>
     <sheet name="lubricants" sheetId="4" r:id="rId4"/>
+    <sheet name="Brands" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="187">
   <si>
     <t>id</t>
   </si>
@@ -547,6 +548,51 @@
   </si>
   <si>
     <t>Enhanced steering tyre</t>
+  </si>
+  <si>
+    <t>slug</t>
+  </si>
+  <si>
+    <t>MRF</t>
+  </si>
+  <si>
+    <t>brand1.png</t>
+  </si>
+  <si>
+    <t>Apollo</t>
+  </si>
+  <si>
+    <t>brand2.png</t>
+  </si>
+  <si>
+    <t>CEAT</t>
+  </si>
+  <si>
+    <t>brand3.png</t>
+  </si>
+  <si>
+    <t>JK</t>
+  </si>
+  <si>
+    <t>brand4.png</t>
+  </si>
+  <si>
+    <t>TVS</t>
+  </si>
+  <si>
+    <t>brand5.png</t>
+  </si>
+  <si>
+    <t>Michelin</t>
+  </si>
+  <si>
+    <t>brand6.png</t>
+  </si>
+  <si>
+    <t>Pirelli</t>
+  </si>
+  <si>
+    <t>brand7.png</t>
   </si>
 </sst>
 </file>
@@ -2772,4 +2818,107 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DBB00C-DC9C-4930-A108-7D473F6BD159}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/public/products.xlsx
+++ b/public/products.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GAYATRI\OneDrive\Desktop\ecommerce-tyre\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFAFF43-FB45-4EF7-942F-DC898E262D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203C713E-E631-4FDB-82AC-47494A0846AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="10080" activeTab="1" xr2:uid="{753CF4C0-B9A8-4CBB-A6D1-A0D84C211A7C}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="10080" activeTab="4" xr2:uid="{753CF4C0-B9A8-4CBB-A6D1-A0D84C211A7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Accessories" sheetId="1" r:id="rId1"/>
     <sheet name="Tyres" sheetId="2" r:id="rId2"/>
     <sheet name="Batteries" sheetId="3" r:id="rId3"/>
     <sheet name="lubricants" sheetId="4" r:id="rId4"/>
+    <sheet name="Brands" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="187">
   <si>
     <t>id</t>
   </si>
@@ -547,6 +548,51 @@
   </si>
   <si>
     <t>Enhanced steering tyre</t>
+  </si>
+  <si>
+    <t>slug</t>
+  </si>
+  <si>
+    <t>MRF</t>
+  </si>
+  <si>
+    <t>brand1.png</t>
+  </si>
+  <si>
+    <t>Apollo</t>
+  </si>
+  <si>
+    <t>brand2.png</t>
+  </si>
+  <si>
+    <t>CEAT</t>
+  </si>
+  <si>
+    <t>brand3.png</t>
+  </si>
+  <si>
+    <t>JK</t>
+  </si>
+  <si>
+    <t>brand4.png</t>
+  </si>
+  <si>
+    <t>TVS</t>
+  </si>
+  <si>
+    <t>brand5.png</t>
+  </si>
+  <si>
+    <t>Michelin</t>
+  </si>
+  <si>
+    <t>brand6.png</t>
+  </si>
+  <si>
+    <t>Pirelli</t>
+  </si>
+  <si>
+    <t>brand7.png</t>
   </si>
 </sst>
 </file>
@@ -2772,4 +2818,112 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FB65D2C-7F0D-4AA2-B850-9117ECEF7D1A}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="2"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>